--- a/src/main/com/py/ipe/resources/QAChatbot.xlsx
+++ b/src/main/com/py/ipe/resources/QAChatbot.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shrut\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shrut\IdeaProjects\new\integrated-platform-environment\src\main\com\py\ipe\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AED78CD-F192-4D10-958F-4182C96351C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D3B813-348B-4907-AECA-7E993EC83167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Question</t>
   </si>
@@ -42,9 +42,6 @@
     <t>What is IPE</t>
   </si>
   <si>
-    <t>IPE is integrated platform environment</t>
-  </si>
-  <si>
     <t>How are you</t>
   </si>
   <si>
@@ -55,6 +52,15 @@
   </si>
   <si>
     <t>My name is Data Dynamo Chatbot</t>
+  </si>
+  <si>
+    <t>What does Data Dynamo Ai Agents do</t>
+  </si>
+  <si>
+    <t>Deploy Ai Agents for Platform stability and SRE. AI Agents are tactically placed to provide a 4 quadrant solution by eliminating issues, create efficiency, reduce redundancy by corelation and does automation for resolution</t>
+  </si>
+  <si>
+    <t>IPE is integrated platform environment, a one stop solution for platform engineer to maintain platform stability and standards powered by Data Dynamo AI Agents</t>
   </si>
 </sst>
 </file>
@@ -372,7 +378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -400,23 +406,31 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
